--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P257"/>
+  <dimension ref="A1:P258"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2697,12 +2697,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Dasykaluta rosamondae</t>
+          <t>Dasycercus cristicauda/blythi</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Dasykaluta rosamondae</t>
+          <t>Dasycercus cristicauda/blythi</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -2739,12 +2739,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Dasyuroides byrnei</t>
+          <t>Dasykaluta rosamondae</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Dasyuroides byrnei</t>
+          <t>Dasykaluta rosamondae</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>21</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -2781,12 +2781,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Dasyurus geoffroii</t>
+          <t>Dasyuroides byrnei</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Dasyurus geoffroii</t>
+          <t>Dasyuroides byrnei</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -2801,10 +2801,20 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -2813,12 +2823,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Dasyurus hallucatus</t>
+          <t>Dasyurus geoffroii</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Dasyurus hallucatus</t>
+          <t>Dasyurus geoffroii</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -2833,7 +2843,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -2845,12 +2855,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Dasyurus viverrinus</t>
+          <t>Dasyurus hallucatus</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dasyurus viverrinus</t>
+          <t>Dasyurus hallucatus</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -2865,7 +2875,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -2877,12 +2887,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Dasyurus viverrinus</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Dasyurus viverrinus</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -2897,20 +2907,10 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -2919,113 +2919,113 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Delphinapterus leucas</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Delphinapterus leucas</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Lyamin et al. 2008 (cetacean slow-wave sleep)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>68.1</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Lyamin et al. 2008 (cetacean slow-wave sleep)</t>
+          <t>Delichon urbicum</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Dendrohyrax sp.</t>
+          <t>Delphinapterus leucas</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Dendrohyrax sp.</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Delphinapterus leucas</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Lyamin et al. 2008 (cetacean slow-wave sleep)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>68.1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Lyamin et al. 2008 (cetacean slow-wave sleep)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Drepanoptila holosericea</t>
+          <t>Dendrohyrax sp.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Drepanoptila holosericea</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>24.8</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+          <t>Dendrohyrax sp.</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Dromiciops gliroides</t>
+          <t>Drepanoptila holosericea</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Dromiciops gliroides</t>
+          <t>Drepanoptila holosericea</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>HIB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -3057,12 +3057,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Echinops telfairi</t>
+          <t>Dromiciops gliroides</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Echinops telfairi</t>
+          <t>Dromiciops gliroides</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>144</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -3099,12 +3099,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Elephantulus edwardii</t>
+          <t>Echinops telfairi</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Elephantulus edwardii</t>
+          <t>Echinops telfairi</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>264</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -3141,12 +3141,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Elephantulus myurus</t>
+          <t>Elephantulus edwardii</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Elephantulus myurus</t>
+          <t>Elephantulus edwardii</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>44</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -3183,17 +3183,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Elephantulus rozeti</t>
+          <t>Elephantulus myurus</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Elephantulus rozeti</t>
+          <t>Elephantulus myurus</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>HIB</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>39</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -3225,12 +3225,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Elephantulus rupestris</t>
+          <t>Elephantulus rozeti</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Elephantulus rupestris</t>
+          <t>Elephantulus rozeti</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -3267,17 +3267,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Eliomys quercinus</t>
+          <t>Elephantulus rupestris</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Eliomys quercinus</t>
+          <t>Elephantulus rupestris</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>HIB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -3309,12 +3309,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Eptesicus fuscus</t>
+          <t>Eliomys quercinus</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Eptesicus fuscus</t>
+          <t>Eliomys quercinus</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>480</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -3351,22 +3351,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Eptesicus fuscus</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>13.96</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Eptesicus fuscus</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -3381,7 +3371,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -3391,7 +3381,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>600</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -3403,66 +3393,86 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Erythrocebus patas</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Erythrocebus patas</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Erinaceus europaeus</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>13.96</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Eugenes fulgens</t>
+          <t>Erythrocebus patas</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Eugenes fulgens</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+          <t>Erythrocebus patas</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Eulampis jugularis</t>
+          <t>Eugenes fulgens</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Eulampis jugularis</t>
+          <t>Eugenes fulgens</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -3477,7 +3487,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -3489,34 +3499,44 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Eulemur fulvus</t>
+          <t>Eulampis jugularis</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Eulemur fulvus</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Eulampis jugularis</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Eulemur macaco</t>
+          <t>Eulemur fulvus</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Eulemur macaco</t>
+          <t>Eulemur fulvus</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3533,17 +3553,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Eulemur mongoz</t>
+          <t>Eulemur macaco</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Eulemur mongoz</t>
+          <t>Eulemur macaco</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3555,54 +3575,34 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Eupetomena macroura</t>
+          <t>Eulemur mongoz</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Eupetomena macroura</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+          <t>Eulemur mongoz</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Fukomys damarensis</t>
+          <t>Eupetomena macroura</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Fukomys damarensis</t>
+          <t>Eupetomena macroura</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -3617,10 +3617,20 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -3629,12 +3639,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Galago moholi</t>
+          <t>Fukomys damarensis</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Galago moholi</t>
+          <t>Fukomys damarensis</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -3649,20 +3659,10 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -3671,66 +3671,76 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Galago senegalensis</t>
+          <t>Galago moholi</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Galago senegalensis</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Galago moholi</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>21.8</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Geogale aurita</t>
+          <t>Galago senegalensis</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Geogale aurita</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+          <t>Galago senegalensis</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Gerbillus pusillus</t>
+          <t>Geogale aurita</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Gerbillus pusillus</t>
+          <t>Geogale aurita</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -3745,20 +3755,10 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -3767,66 +3767,76 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Giraffa camelopardalis</t>
+          <t>Gerbillus pusillus</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Giraffa camelopardalis</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>3.44</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Gerbillus pusillus</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Glirulus japonicus</t>
+          <t>Giraffa camelopardalis</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Glirulus japonicus</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>HIB</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+          <t>Giraffa camelopardalis</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Glis glis</t>
+          <t>Glirulus japonicus</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Glis glis</t>
+          <t>Glirulus japonicus</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -3839,19 +3849,9 @@
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>380</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -3863,17 +3863,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Glossophaga soricina</t>
+          <t>Glis glis</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Glossophaga soricina</t>
+          <t>Glis glis</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>HIB</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>977</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -3905,12 +3905,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Gracilinanus agilis</t>
+          <t>Glossophaga soricina</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Gracilinanus agilis</t>
+          <t>Glossophaga soricina</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -3925,10 +3925,20 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -3937,17 +3947,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Graphiurus murinus</t>
+          <t>Gracilinanus agilis</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Graphiurus murinus</t>
+          <t>Gracilinanus agilis</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>HIB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -3957,20 +3967,10 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -3979,12 +3979,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Graphiurus ocularis</t>
+          <t>Graphiurus murinus</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Graphiurus ocularis</t>
+          <t>Graphiurus murinus</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -3997,9 +3997,19 @@
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>192</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -4011,12 +4021,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Hipposideros terasensis</t>
+          <t>Graphiurus ocularis</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Hipposideros terasensis</t>
+          <t>Graphiurus ocularis</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -4029,19 +4039,9 @@
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>13.8</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>312</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -4053,17 +4053,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Hirundapus caudacutus</t>
+          <t>Hipposideros terasensis</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Hirundapus caudacutus</t>
+          <t>Hipposideros terasensis</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>HIB</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>456</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -4095,165 +4095,165 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Homo sapiens</t>
+          <t>Hirundapus caudacutus</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>8.47</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Hirundapus caudacutus</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Ictidomys tridecemlineatus</t>
+          <t>Homo sapiens</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ictidomys tridecemlineatus</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>HIB</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>8.47</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Inia geoffrensis</t>
+          <t>Ictidomys tridecemlineatus</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Inia geoffrensis</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Lyamin et al. 2008 (cetacean slow-wave sleep)</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>71.9</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>Lyamin et al. 2008 (cetacean slow-wave sleep)</t>
+          <t>Ictidomys tridecemlineatus</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Jaculus orientalis</t>
+          <t>Inia geoffrensis</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Jaculus orientalis</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>HIB</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+          <t>Inia geoffrensis</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Lyamin et al. 2008 (cetacean slow-wave sleep)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Lyamin et al. 2008 (cetacean slow-wave sleep)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Lampornis clemenciae</t>
+          <t>Jaculus orientalis</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Lampornis clemenciae</t>
+          <t>Jaculus orientalis</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>HIB</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -4263,10 +4263,20 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -4275,17 +4285,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Lasiurus borealis</t>
+          <t>Lampornis clemenciae</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Lasiurus borealis</t>
+          <t>Lampornis clemenciae</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>HIB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -4295,20 +4305,10 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -4317,12 +4317,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Lasiurus cinereus</t>
+          <t>Lasiurus borealis</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Lasiurus cinereus</t>
+          <t>Lasiurus borealis</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>260</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -4359,61 +4359,81 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Loxodonta africana</t>
+          <t>Lasiurus cinereus</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Loxodonta africana</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Lasiurus cinereus</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Macaca arctoides</t>
+          <t>Loxodonta africana</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Macaca arctoides</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Loxodonta africana</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Macaca fascicularis</t>
+          <t>Macaca arctoides</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Macaca fascicularis</t>
+          <t>Macaca arctoides</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4425,162 +4445,142 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Macaca mulatta</t>
+          <t>Macaca fascicularis</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Macaca mulatta</t>
+          <t>Macaca fascicularis</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
           <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>8.74</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Macaca nemestrina</t>
+          <t>Macaca mulatta</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Macaca nemestrina</t>
+          <t>Macaca mulatta</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
           <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>8.74</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Macaca radiata</t>
+          <t>Macaca nemestrina</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Macaca radiata</t>
+          <t>Macaca nemestrina</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
           <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>9.02</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Macaca sylvanus</t>
+          <t>Macaca radiata</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Macaca sylvanus</t>
+          <t>Macaca radiata</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
           <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>9.02</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Macroglossus minimus</t>
+          <t>Macaca sylvanus</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Macroglossus minimus</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>21.6</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="P119" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+          <t>Macaca sylvanus</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Macroscelides proboscideus</t>
+          <t>Macroglossus minimus</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Macroscelides proboscideus</t>
+          <t>Macroglossus minimus</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -4617,12 +4617,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Manacus vitellinus</t>
+          <t>Macroscelides proboscideus</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Manacus vitellinus</t>
+          <t>Macroscelides proboscideus</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -4659,12 +4659,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Marmosa microtarsus</t>
+          <t>Manacus vitellinus</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Marmosa microtarsus</t>
+          <t>Manacus vitellinus</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -4701,17 +4701,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Marmota broweri</t>
+          <t>Marmosa microtarsus</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Marmota broweri</t>
+          <t>Marmosa microtarsus</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>HIB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -4719,9 +4719,19 @@
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -4733,12 +4743,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Marmota flaviventris</t>
+          <t>Marmota broweri</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Marmota flaviventris</t>
+          <t>Marmota broweri</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -4751,19 +4761,9 @@
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>480</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -4775,12 +4775,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Marmota marmota</t>
+          <t>Marmota flaviventris</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Marmota marmota</t>
+          <t>Marmota flaviventris</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>360</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -4817,12 +4817,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Marmota monax</t>
+          <t>Marmota marmota</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Marmota monax</t>
+          <t>Marmota marmota</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>353</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -4859,17 +4859,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Megaloglossus woermanni</t>
+          <t>Marmota monax</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Megaloglossus woermanni</t>
+          <t>Marmota monax</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>HIB</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -4879,10 +4879,20 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -4891,12 +4901,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Melanotrochilus fuscus</t>
+          <t>Megaloglossus woermanni</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Melanotrochilus fuscus</t>
+          <t>Megaloglossus woermanni</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -4911,20 +4921,10 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>11.2</t>
-        </is>
-      </c>
-      <c r="P128" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -4933,17 +4933,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Meles meles</t>
+          <t>Melanotrochilus fuscus</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Meles meles</t>
+          <t>Melanotrochilus fuscus</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>HIB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -4953,10 +4953,20 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -4965,17 +4975,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Mephitis mephitis</t>
+          <t>Meles meles</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Mephitis mephitis</t>
+          <t>Meles meles</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>HIB</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -4985,20 +4995,10 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O130" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="P130" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -5007,27 +5007,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Mesocricetus auratus</t>
+          <t>Mephitis mephitis</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Mesocricetus auratus</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>14.98</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Mephitis mephitis</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>HIB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -5037,7 +5027,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>26</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -5047,7 +5037,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -5059,12 +5049,22 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Mesocricetus brandti</t>
+          <t>Mesocricetus auratus</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Mesocricetus brandti</t>
+          <t>Mesocricetus auratus</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>14.98</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -5077,9 +5077,19 @@
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>264</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -5091,12 +5101,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Microcebus griseorufus</t>
+          <t>Mesocricetus brandti</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Microcebus griseorufus</t>
+          <t>Mesocricetus brandti</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -5109,19 +5119,9 @@
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>144</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -5133,27 +5133,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Microcebus murinus</t>
+          <t>Microcebus griseorufus</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Microcebus murinus</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Microcebus griseorufus</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>HIB</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -5163,7 +5153,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -5173,7 +5163,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -5185,12 +5175,22 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Microcebus myoxinus</t>
+          <t>Microcebus murinus</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Microcebus myoxinus</t>
+          <t>Microcebus murinus</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -5227,12 +5227,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Microcebus ravelobensis</t>
+          <t>Microcebus myoxinus</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Microcebus ravelobensis</t>
+          <t>Microcebus myoxinus</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="P136" t="inlineStr">
@@ -5269,17 +5269,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Microdipodops pallidus</t>
+          <t>Microcebus ravelobensis</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Microdipodops pallidus</t>
+          <t>Microcebus ravelobensis</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>HIB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>25</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -5311,17 +5311,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Microgale dobsoni</t>
+          <t>Microdipodops pallidus</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Microgale dobsoni</t>
+          <t>Microdipodops pallidus</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>HIB</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -5331,10 +5331,20 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -5343,17 +5353,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Miniopterus schreibersii</t>
+          <t>Microgale dobsoni</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Miniopterus schreibersii</t>
+          <t>Microgale dobsoni</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>HIB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -5363,20 +5373,10 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O139" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="P139" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -5385,12 +5385,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Mops condylurus</t>
+          <t>Miniopterus schreibersii</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Mops condylurus</t>
+          <t>Miniopterus schreibersii</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -5405,10 +5405,20 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -5417,27 +5427,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Mus musculus</t>
+          <t>Mops condylurus</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Mus musculus</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>11.6</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Mops condylurus</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>HIB</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -5447,20 +5447,10 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O141" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P141" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -5469,17 +5459,27 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Muscardinus avellanarius</t>
+          <t>Mus musculus</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Muscardinus avellanarius</t>
+          <t>Mus musculus</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>HIB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -5511,12 +5511,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Myotis adversus</t>
+          <t>Muscardinus avellanarius</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Myotis adversus</t>
+          <t>Muscardinus avellanarius</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>624</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -5553,12 +5553,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Myotis lucifugus</t>
+          <t>Myotis adversus</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Myotis lucifugus</t>
+          <t>Myotis adversus</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>1152</t>
+          <t>192</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -5595,12 +5595,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Myotis myotis</t>
+          <t>Myotis lucifugus</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Myotis myotis</t>
+          <t>Myotis lucifugus</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -5637,12 +5637,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Myotis nattereri</t>
+          <t>Myotis myotis</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Myotis nattereri</t>
+          <t>Myotis myotis</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -5679,12 +5679,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Myotis velifer</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Myotis velifer</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -5699,10 +5699,20 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -5711,17 +5721,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Myrmecobius fasciatus</t>
+          <t>Myotis velifer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Myrmecobius fasciatus</t>
+          <t>Myotis velifer</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>HIB</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -5731,20 +5741,10 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>15.3</t>
-        </is>
-      </c>
-      <c r="P148" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -5753,12 +5753,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Nectarinia famosa</t>
+          <t>Myrmecobius fasciatus</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Nectarinia famosa</t>
+          <t>Myrmecobius fasciatus</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -5795,12 +5795,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Ningaui yvonnae</t>
+          <t>Nectarinia famosa</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ningaui yvonnae</t>
+          <t>Nectarinia famosa</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -5837,12 +5837,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Notiosorex crawfordi</t>
+          <t>Ningaui yvonnae</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Notiosorex crawfordi</t>
+          <t>Ningaui yvonnae</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -5857,10 +5857,20 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -5869,17 +5879,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Notiosorex crawfordi</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Notiosorex crawfordi</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>HIB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -5889,7 +5899,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -5901,17 +5911,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Nycteris thebaica</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Nycteris thebaica</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>HIB</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -5921,7 +5931,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -5933,12 +5943,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Nyctimene albiventer</t>
+          <t>Nycteris thebaica</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Nyctimene albiventer</t>
+          <t>Nycteris thebaica</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -5953,7 +5963,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>27</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -5965,17 +5975,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Nyctophilus bifax</t>
+          <t>Nyctimene albiventer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Nyctophilus bifax</t>
+          <t>Nyctimene albiventer</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>HIB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -5985,20 +5995,10 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O155" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="P155" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -6007,12 +6007,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Nyctophilus geoffroyi</t>
+          <t>Nyctophilus bifax</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Nyctophilus geoffroyi</t>
+          <t>Nyctophilus bifax</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -6027,7 +6027,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>129</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -6049,12 +6049,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Nyctophilus gouldi</t>
+          <t>Nyctophilus geoffroyi</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Nyctophilus gouldi</t>
+          <t>Nyctophilus geoffroyi</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>362</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
@@ -6091,17 +6091,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Oreotrochilus estella</t>
+          <t>Nyctophilus gouldi</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Oreotrochilus estella</t>
+          <t>Nyctophilus gouldi</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>HIB</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -6111,10 +6111,20 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -6123,12 +6133,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Orthorhynchus cristatus</t>
+          <t>Oreotrochilus estella</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Orthorhynchus cristatus</t>
+          <t>Oreotrochilus estella</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -6143,7 +6153,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -6155,211 +6165,221 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Oryctolagus cuniculus</t>
+          <t>Orthorhynchus cristatus</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Oryctolagus cuniculus</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>9.55</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Orthorhynchus cristatus</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Otus senegalensis</t>
+          <t>Oryctolagus cuniculus</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Otus senegalensis</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O161" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P161" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+          <t>Oryctolagus cuniculus</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>9.55</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Pan troglodytes</t>
+          <t>Otus senegalensis</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Pan troglodytes</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Otus senegalensis</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Panterpe insignis</t>
+          <t>Pan troglodytes</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Panterpe insignis</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N163" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+          <t>Pan troglodytes</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Papio anubis</t>
+          <t>Panterpe insignis</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Papio anubis</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Panterpe insignis</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Papio cynocephalus</t>
+          <t>Papio anubis</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Papio cynocephalus</t>
+          <t>Papio anubis</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
           <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>6.19</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Papio hamadryas</t>
+          <t>Papio cynocephalus</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Papio hamadryas</t>
+          <t>Papio cynocephalus</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
           <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>6.19</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Papio papio</t>
+          <t>Papio hamadryas</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Papio papio</t>
+          <t>Papio hamadryas</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -6371,54 +6391,34 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Perognathus californicus</t>
+          <t>Papio papio</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Perognathus californicus</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O168" t="inlineStr">
-        <is>
-          <t>15.4</t>
-        </is>
-      </c>
-      <c r="P168" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+          <t>Papio papio</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Perognathus fasciatus</t>
+          <t>Perognathus californicus</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Perognathus fasciatus</t>
+          <t>Perognathus californicus</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -6455,17 +6455,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Perognathus longimembris</t>
+          <t>Perognathus fasciatus</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Perognathus longimembris</t>
+          <t>Perognathus fasciatus</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>HIB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -6497,12 +6497,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Perognathus parvus</t>
+          <t>Perognathus longimembris</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Perognathus parvus</t>
+          <t>Perognathus longimembris</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>112</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -6539,17 +6539,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Peromyscus boylii</t>
+          <t>Perognathus parvus</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Peromyscus boylii</t>
+          <t>Perognathus parvus</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>HIB</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>192</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -6581,12 +6581,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Peromyscus crinitus</t>
+          <t>Peromyscus boylii</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Peromyscus crinitus</t>
+          <t>Peromyscus boylii</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -6623,12 +6623,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Peromyscus eremicus</t>
+          <t>Peromyscus crinitus</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Peromyscus eremicus</t>
+          <t>Peromyscus crinitus</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -6665,12 +6665,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Peromyscus gossypinus</t>
+          <t>Peromyscus eremicus</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Peromyscus gossypinus</t>
+          <t>Peromyscus eremicus</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -6685,10 +6685,20 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -6697,12 +6707,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Peromyscus leucopus</t>
+          <t>Peromyscus gossypinus</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Peromyscus leucopus</t>
+          <t>Peromyscus gossypinus</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -6717,20 +6727,10 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O176" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="P176" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -6739,12 +6739,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Peromyscus maniculatus</t>
+          <t>Peromyscus leucopus</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Peromyscus maniculatus</t>
+          <t>Peromyscus leucopus</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -6781,12 +6781,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Petaurus breviceps</t>
+          <t>Peromyscus maniculatus</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Petaurus breviceps</t>
+          <t>Peromyscus maniculatus</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -6823,12 +6823,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Petromyscus collinus</t>
+          <t>Petaurus breviceps</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Petromyscus collinus</t>
+          <t>Petaurus breviceps</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -6843,10 +6843,20 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -6855,17 +6865,17 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Phalaenoptilus nuttallii</t>
+          <t>Petromyscus collinus</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Phalaenoptilus nuttallii</t>
+          <t>Petromyscus collinus</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>HIB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -6875,20 +6885,10 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O180" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="P180" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -6897,86 +6897,86 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Phocoena phocoena</t>
+          <t>Phalaenoptilus nuttallii</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Phocoena phocoena</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>46.4</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Lyamin et al. 2008 (cetacean slow-wave sleep)</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>Lyamin et al. 2008 (cetacean slow-wave sleep)</t>
+          <t>Phalaenoptilus nuttallii</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Phodopus sungorus</t>
+          <t>Phocoena phocoena</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Phodopus sungorus</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>12.3</t>
-        </is>
-      </c>
-      <c r="N182" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O182" t="inlineStr">
-        <is>
-          <t>13.8</t>
-        </is>
-      </c>
-      <c r="P182" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+          <t>Phocoena phocoena</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>46.4</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Lyamin et al. 2008 (cetacean slow-wave sleep)</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Lyamin et al. 2008 (cetacean slow-wave sleep)</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Phyllotis darwini</t>
+          <t>Phodopus sungorus</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Phyllotis darwini</t>
+          <t>Phodopus sungorus</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -7013,17 +7013,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Pipistrellus pipistrellus</t>
+          <t>Phyllotis darwini</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Pipistrellus pipistrellus</t>
+          <t>Phyllotis darwini</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>HIB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -7033,10 +7033,20 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -7045,12 +7055,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Pipistrellus subflavus</t>
+          <t>Pipistrellus pipistrellus</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Pipistrellus subflavus</t>
+          <t>Pipistrellus pipistrellus</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -7063,12 +7073,12 @@
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
-      <c r="O185" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="P185" t="inlineStr">
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -7077,17 +7087,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Planigale gilesi</t>
+          <t>Pipistrellus subflavus</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Planigale gilesi</t>
+          <t>Pipistrellus subflavus</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>HIB</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -7095,19 +7105,9 @@
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>14.3</t>
-        </is>
-      </c>
-      <c r="N186" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
@@ -7119,12 +7119,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Planigale ingrami</t>
+          <t>Planigale gilesi</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Planigale ingrami</t>
+          <t>Planigale gilesi</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -7137,9 +7137,19 @@
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
@@ -7151,12 +7161,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Planigale maculata</t>
+          <t>Planigale ingrami</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Planigale maculata</t>
+          <t>Planigale ingrami</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -7169,19 +7179,9 @@
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
-      </c>
-      <c r="N188" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -7193,12 +7193,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Planigale tenuirostris</t>
+          <t>Planigale maculata</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Planigale tenuirostris</t>
+          <t>Planigale maculata</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -7211,9 +7211,19 @@
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
@@ -7225,17 +7235,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Planigale tenuirostris</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Planigale tenuirostris</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>HIB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -7243,12 +7253,12 @@
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="N190" t="inlineStr">
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -7257,17 +7267,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Podargus strigoides</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Podargus strigoides</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>HIB</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -7277,20 +7287,10 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O191" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P191" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -7299,88 +7299,98 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Pongo pygmaeus</t>
+          <t>Podargus strigoides</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Pongo pygmaeus</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Podargus strigoides</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>29.1</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Procavia sp.</t>
+          <t>Pongo pygmaeus</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Procavia sp.</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>5.45</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Pongo pygmaeus</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Proteles cristata</t>
+          <t>Procavia sp.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Proteles cristata</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="L194" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="N194" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+          <t>Procavia sp.</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>5.45</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Pseudantechinus macdonnellensis</t>
+          <t>Proteles cristata</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Pseudantechinus macdonnellensis</t>
+          <t>Proteles cristata</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -7395,20 +7405,10 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>31</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O195" t="inlineStr">
-        <is>
-          <t>14.3</t>
-        </is>
-      </c>
-      <c r="P195" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -7417,81 +7417,81 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Rattus norvegicus</t>
+          <t>Pseudantechinus macdonnellensis</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Rattus norvegicus</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>12.27</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Pseudantechinus macdonnellensis</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>15.9</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Reithrodontomys megalotis</t>
+          <t>Rattus norvegicus</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Reithrodontomys megalotis</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="N197" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O197" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P197" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+          <t>Rattus norvegicus</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>12.27</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Rhinolophus ferrumequinum</t>
+          <t>Reithrodontomys megalotis</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Rhinolophus ferrumequinum</t>
+          <t>Reithrodontomys megalotis</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>HIB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -7523,12 +7523,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Rhinolophus hipposideros</t>
+          <t>Rhinolophus ferrumequinum</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Rhinolophus hipposideros</t>
+          <t>Rhinolophus ferrumequinum</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -7541,9 +7541,19 @@
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>432</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -7555,12 +7565,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Rhinopoma microphyllum</t>
+          <t>Rhinolophus hipposideros</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Rhinopoma microphyllum</t>
+          <t>Rhinolophus hipposideros</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -7573,12 +7583,12 @@
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="N200" t="inlineStr">
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>2064</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -7587,17 +7597,17 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Saccostomus campestris</t>
+          <t>Rhinopoma microphyllum</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Saccostomus campestris</t>
+          <t>Rhinopoma microphyllum</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>HIB</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -7607,20 +7617,10 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O201" t="inlineStr">
-        <is>
-          <t>2.7</t>
-        </is>
-      </c>
-      <c r="P201" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -7629,49 +7629,69 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Saimiri sciureus</t>
+          <t>Saccostomus campestris</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Saimiri sciureus</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>9.11</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Saccostomus campestris</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Scalopus aquaticus</t>
+          <t>Saimiri sciureus</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Scalopus aquaticus</t>
+          <t>Saimiri sciureus</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -7683,54 +7703,34 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Scardafella inca</t>
+          <t>Scalopus aquaticus</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Scardafella inca</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="L204" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="N204" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O204" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P204" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+          <t>Scalopus aquaticus</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Scotophilus dinganii</t>
+          <t>Scardafella inca</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Scotophilus dinganii</t>
+          <t>Scardafella inca</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>29</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -7767,12 +7767,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Scotophilus mhlanganii</t>
+          <t>Scotophilus dinganii</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Scotophilus mhlanganii</t>
+          <t>Scotophilus dinganii</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -7809,12 +7809,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Selasphorus platycercus</t>
+          <t>Scotophilus mhlanganii</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Selasphorus platycercus</t>
+          <t>Scotophilus mhlanganii</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -7829,10 +7829,20 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -7841,12 +7851,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Selasphorus rufus</t>
+          <t>Selasphorus platycercus</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Selasphorus rufus</t>
+          <t>Selasphorus platycercus</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -7861,20 +7871,10 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O208" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P208" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -7883,12 +7883,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Selasphorus sasin</t>
+          <t>Selasphorus rufus</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Selasphorus sasin</t>
+          <t>Selasphorus rufus</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -7903,10 +7903,20 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -7915,17 +7925,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Setifer setosus</t>
+          <t>Selasphorus sasin</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Setifer setosus</t>
+          <t>Selasphorus sasin</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>HIB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -7935,20 +7945,10 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O210" t="inlineStr">
-        <is>
-          <t>3600</t>
-        </is>
-      </c>
-      <c r="P210" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -7957,17 +7957,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Sminthopsis crassicaudata</t>
+          <t>Setifer setosus</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Sminthopsis crassicaudata</t>
+          <t>Setifer setosus</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>HIB</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>19.5</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -7999,12 +7999,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Sminthopsis douglasi</t>
+          <t>Sminthopsis crassicaudata</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Sminthopsis douglasi</t>
+          <t>Sminthopsis crassicaudata</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>19.5</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -8041,12 +8041,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Sminthopsis macroura</t>
+          <t>Sminthopsis douglasi</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Sminthopsis macroura</t>
+          <t>Sminthopsis douglasi</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -8083,12 +8083,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Sminthopsis murina</t>
+          <t>Sminthopsis macroura</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Sminthopsis murina</t>
+          <t>Sminthopsis macroura</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -8125,12 +8125,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Sminthopsis ooldea</t>
+          <t>Sminthopsis murina</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Sminthopsis ooldea</t>
+          <t>Sminthopsis murina</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -8139,6 +8139,26 @@
         </is>
       </c>
       <c r="L215" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -8147,12 +8167,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Sorex sinuosus</t>
+          <t>Sminthopsis ooldea</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Sorex sinuosus</t>
+          <t>Sminthopsis ooldea</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -8161,16 +8181,6 @@
         </is>
       </c>
       <c r="L216" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O216" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P216" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -8179,17 +8189,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Spermophilus armatus</t>
+          <t>Sorex sinuosus</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Spermophilus armatus</t>
+          <t>Sorex sinuosus</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>HIB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -8199,7 +8209,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -8211,12 +8221,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Spermophilus beecheyi</t>
+          <t>Spermophilus armatus</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Spermophilus beecheyi</t>
+          <t>Spermophilus armatus</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -8229,19 +8239,9 @@
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="N218" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>576</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
@@ -8253,12 +8253,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Spermophilus beldingi</t>
+          <t>Spermophilus beecheyi</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Spermophilus beldingi</t>
+          <t>Spermophilus beecheyi</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -8271,9 +8271,19 @@
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>72</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -8285,12 +8295,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Spermophilus citellus</t>
+          <t>Spermophilus beldingi</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Spermophilus citellus</t>
+          <t>Spermophilus beldingi</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -8303,19 +8313,9 @@
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
-      <c r="N220" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>400</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -8327,12 +8327,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Spermophilus columbianus</t>
+          <t>Spermophilus citellus</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Spermophilus columbianus</t>
+          <t>Spermophilus citellus</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -8347,7 +8347,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>415</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
@@ -8369,12 +8369,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Spermophilus dauricus</t>
+          <t>Spermophilus columbianus</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Spermophilus dauricus</t>
+          <t>Spermophilus columbianus</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>424</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
@@ -8411,12 +8411,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Spermophilus elegans</t>
+          <t>Spermophilus dauricus</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Spermophilus elegans</t>
+          <t>Spermophilus dauricus</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -8429,9 +8429,19 @@
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>-2.4</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>377</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
@@ -8443,12 +8453,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Spermophilus lateralis</t>
+          <t>Spermophilus elegans</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Spermophilus lateralis</t>
+          <t>Spermophilus elegans</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -8461,19 +8471,9 @@
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>-1</t>
-        </is>
-      </c>
-      <c r="N224" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>450</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -8485,12 +8485,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Spermophilus mexicanus</t>
+          <t>Spermophilus lateralis</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Spermophilus mexicanus</t>
+          <t>Spermophilus lateralis</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-1</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>504</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -8527,12 +8527,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Spermophilus parryii</t>
+          <t>Spermophilus mexicanus</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Spermophilus parryii</t>
+          <t>Spermophilus mexicanus</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -8547,7 +8547,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -8569,12 +8569,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Spermophilus richardsonii</t>
+          <t>Spermophilus parryii</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Spermophilus richardsonii</t>
+          <t>Spermophilus parryii</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>550</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -8611,12 +8611,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Spermophilus saturatus</t>
+          <t>Spermophilus richardsonii</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Spermophilus saturatus</t>
+          <t>Spermophilus richardsonii</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>456</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -8653,12 +8653,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Spermophilus tereticaudus</t>
+          <t>Spermophilus saturatus</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Spermophilus tereticaudus</t>
+          <t>Spermophilus saturatus</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -8671,9 +8671,19 @@
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>360</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -8685,12 +8695,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Spermophilus variegatus</t>
+          <t>Spermophilus tereticaudus</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Spermophilus variegatus</t>
+          <t>Spermophilus tereticaudus</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -8703,19 +8713,9 @@
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N230" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -8727,12 +8727,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Spermophilus xanthoprymnus</t>
+          <t>Spermophilus variegatus</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Spermophilus xanthoprymnus</t>
+          <t>Spermophilus variegatus</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -8747,7 +8747,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>172</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
@@ -8769,17 +8769,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Steatomys pratensis</t>
+          <t>Spermophilus xanthoprymnus</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Steatomys pratensis</t>
+          <t>Spermophilus xanthoprymnus</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>HIB</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>468</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
@@ -8811,12 +8811,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Sturnira lilium</t>
+          <t>Steatomys pratensis</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Sturnira lilium</t>
+          <t>Steatomys pratensis</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -8831,10 +8831,20 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>16.9</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -8843,12 +8853,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Suncus etruscus</t>
+          <t>Sturnira lilium</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Suncus etruscus</t>
+          <t>Sturnira lilium</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -8863,20 +8873,10 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O234" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
-      </c>
-      <c r="P234" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -8885,81 +8885,81 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Sus scrofa</t>
+          <t>Suncus etruscus</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Sus scrofa</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Suncus etruscus</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Syconycteris australis</t>
+          <t>Sus scrofa</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Syconycteris australis</t>
-        </is>
-      </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="L236" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>17.2</t>
-        </is>
-      </c>
-      <c r="N236" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O236" t="inlineStr">
+          <t>Sus scrofa</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="P236" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Tachyglossus aculeatus</t>
+          <t>Syconycteris australis</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Tachyglossus aculeatus</t>
+          <t>Syconycteris australis</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>HIB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
@@ -8991,12 +8991,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Tadarida aegyptiaca</t>
+          <t>Tachyglossus aculeatus</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Tadarida aegyptiaca</t>
+          <t>Tachyglossus aculeatus</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>648</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
@@ -9033,12 +9033,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Tadarida brasiliensis</t>
+          <t>Tadarida aegyptiaca</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Tadarida brasiliensis</t>
+          <t>Tadarida aegyptiaca</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -9053,10 +9053,20 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -9065,12 +9075,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Tadarida teniotis</t>
+          <t>Tadarida brasiliensis</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Tadarida teniotis</t>
+          <t>Tadarida brasiliensis</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -9085,20 +9095,10 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O240" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="P240" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -9107,12 +9107,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Tamias amoenus</t>
+          <t>Tadarida teniotis</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Tamias amoenus</t>
+          <t>Tadarida teniotis</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>192</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
@@ -9149,12 +9149,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Tamias striatus</t>
+          <t>Tamias amoenus</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Tamias striatus</t>
+          <t>Tamias amoenus</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>312</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
@@ -9191,17 +9191,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Tarsipes rostratus</t>
+          <t>Tamias striatus</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Tarsipes rostratus</t>
+          <t>Tamias striatus</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>HIB</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
@@ -9233,12 +9233,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Taxidea taxus</t>
+          <t>Tarsipes rostratus</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Taxidea taxus</t>
+          <t>Tarsipes rostratus</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
@@ -9275,17 +9275,17 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Tenrec ecaudatus</t>
+          <t>Taxidea taxus</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Tenrec ecaudatus</t>
+          <t>Taxidea taxus</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>HIB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>28</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -9305,7 +9305,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>6480</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
@@ -9317,17 +9317,17 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Thylamys elegans</t>
+          <t>Tenrec ecaudatus</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Thylamys elegans</t>
+          <t>Tenrec ecaudatus</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>DT</t>
+          <t>HIB</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -9347,7 +9347,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
@@ -9359,12 +9359,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Todus mexicanus</t>
+          <t>Thylamys elegans</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Todus mexicanus</t>
+          <t>Thylamys elegans</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -9379,10 +9379,20 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -9391,98 +9401,98 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Tupaia sp.</t>
+          <t>Todus mexicanus</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Tupaia sp.</t>
-        </is>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>15.84</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Todus mexicanus</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Tursiops truncatus</t>
+          <t>Tupaia sp.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Tursiops truncatus</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>33.9</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>Lyamin et al. 2008 (cetacean slow-wave sleep)</t>
-        </is>
-      </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t>88.2</t>
-        </is>
-      </c>
-      <c r="J249" t="inlineStr">
-        <is>
-          <t>Lyamin et al. 2008 (cetacean slow-wave sleep)</t>
+          <t>Tupaia sp.</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>15.84</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Urocolius indicus</t>
+          <t>Tursiops truncatus</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Urocolius indicus</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t>DT</t>
-        </is>
-      </c>
-      <c r="L250" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O250" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P250" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+          <t>Tursiops truncatus</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>33.9</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Lyamin et al. 2008 (cetacean slow-wave sleep)</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>Lyamin et al. 2008 (cetacean slow-wave sleep)</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Urocolius macrourus</t>
+          <t>Urocolius indicus</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Urocolius macrourus</t>
+          <t>Urocolius indicus</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -9495,19 +9505,9 @@
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="N251" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P251" t="inlineStr">
@@ -9519,17 +9519,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Ursus americanus</t>
+          <t>Urocolius macrourus</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Ursus americanus</t>
+          <t>Urocolius macrourus</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>HIB</t>
+          <t>DT</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -9539,10 +9539,20 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>22</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -9551,12 +9561,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Ursus arctos</t>
+          <t>Ursus americanus</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Ursus arctos</t>
+          <t>Ursus americanus</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -9571,7 +9581,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -9583,12 +9593,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Vespadelus vulturnus</t>
+          <t>Ursus arctos</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Vespadelus vulturnus</t>
+          <t>Ursus arctos</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -9603,7 +9613,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -9615,12 +9625,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Zaedyus pichiy</t>
+          <t>Vespadelus vulturnus</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Zaedyus pichiy</t>
+          <t>Vespadelus vulturnus</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -9635,20 +9645,10 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O255" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="P255" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -9657,12 +9657,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Zapus hudsonius</t>
+          <t>Zaedyus pichiy</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Zapus hudsonius</t>
+          <t>Zaedyus pichiy</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -9675,9 +9675,19 @@
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>112</t>
         </is>
       </c>
       <c r="P256" t="inlineStr">
@@ -9689,40 +9699,72 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
+          <t>Zapus hudsonius</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Zapus hudsonius</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
           <t>Zapus princeps</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B258" t="inlineStr">
         <is>
           <t>Zapus princeps</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr">
+      <c r="K258" t="inlineStr">
         <is>
           <t>HIB</t>
         </is>
       </c>
-      <c r="L257" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="M257" t="inlineStr">
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
       </c>
-      <c r="N257" t="inlineStr">
-        <is>
-          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
-        </is>
-      </c>
-      <c r="O257" t="inlineStr">
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
         <is>
           <t>650</t>
         </is>
       </c>
-      <c r="P257" t="inlineStr">
+      <c r="P258" t="inlineStr">
         <is>
           <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
@@ -10009,13 +10051,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44E07C5D-1FCA-48D9-8A41-CD18B54C91FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9E1C4EC-C43C-4EA7-8D5E-F1EB30597206}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AC2E086-8169-41BF-B35E-EE25319C3540}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60CC22A5-AC30-472C-A2FA-46984DF14C24}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{076AF987-FDC8-41C3-B63F-E4BE33E1FE45}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A035E43-8267-4539-A8DF-1F131AF24A54}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -10051,13 +10051,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9E1C4EC-C43C-4EA7-8D5E-F1EB30597206}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C4EFE54-2EBA-448D-8103-410BE15617A0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60CC22A5-AC30-472C-A2FA-46984DF14C24}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6423480-7A5A-4992-B2ED-1CA475B4AC4C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A035E43-8267-4539-A8DF-1F131AF24A54}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A3FDCD2-CC8C-40CF-8021-1497DF968E6A}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -10051,13 +10051,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C4EFE54-2EBA-448D-8103-410BE15617A0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCB502B9-BF12-413F-B0DB-64A313C0789B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6423480-7A5A-4992-B2ED-1CA475B4AC4C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8840112C-A033-425A-9AB1-02287FCA0F69}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A3FDCD2-CC8C-40CF-8021-1497DF968E6A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43C13BEE-E30F-4A8C-BA14-1032962FB2CF}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -10051,13 +10051,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCB502B9-BF12-413F-B0DB-64A313C0789B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A59AEB9-43C0-49D3-925E-119318758878}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8840112C-A033-425A-9AB1-02287FCA0F69}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{480F9818-82E9-485C-B600-3B67F8B6732E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43C13BEE-E30F-4A8C-BA14-1032962FB2CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21FF0449-96A8-4E96-8DEA-54ABAF328DBE}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -7990,13 +7990,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1902F521-F7F7-4215-9694-49D421A8D42E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5925274D-5C55-41D1-96BD-24C7D226070B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C2AAF3F-0A72-48F9-8B1F-90E9ACB32A4E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65893EF3-2FDE-4BAA-802F-4C5ED343FAF2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A42322F-EFD1-451C-B6B9-D22C3BDCC389}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{414BA9F6-FD46-4480-A8E3-35D1616DC71D}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -7990,13 +7990,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5925274D-5C55-41D1-96BD-24C7D226070B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EBB07A1-BB95-457D-92F2-57E11107D391}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65893EF3-2FDE-4BAA-802F-4C5ED343FAF2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73180932-E0BD-4D2A-B2B8-C4414BC6A238}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{414BA9F6-FD46-4480-A8E3-35D1616DC71D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75339DD9-3F2E-43E2-9F11-AAF51E6A8145}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -7712,291 +7712,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EBB07A1-BB95-457D-92F2-57E11107D391}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73180932-E0BD-4D2A-B2B8-C4414BC6A238}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75339DD9-3F2E-43E2-9F11-AAF51E6A8145}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -7712,4 +7712,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3B176F2-02B2-4DA8-B9B2-8CC9FCE3FA7F}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44EAFD4F-41C4-4BD9-8E8D-5BC3170F0B92}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D3C3D28-9FD3-4842-9B04-16C4126A441C}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -7712,291 +7712,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3B176F2-02B2-4DA8-B9B2-8CC9FCE3FA7F}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44EAFD4F-41C4-4BD9-8E8D-5BC3170F0B92}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D3C3D28-9FD3-4842-9B04-16C4126A441C}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -7712,4 +7712,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D783328-52AB-4FCD-9FB2-8FEBE18A9134}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{620A2C7C-F642-4932-9E65-52D7705DBA99}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9C3197E-EB3F-42C2-BE7B-784768EC6759}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -7990,13 +7990,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D783328-52AB-4FCD-9FB2-8FEBE18A9134}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC9CBB06-5AC2-431B-AFA2-BA6F4132E581}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{620A2C7C-F642-4932-9E65-52D7705DBA99}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{963FA2E2-53B5-4F5F-B80F-05476EE4A892}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9C3197E-EB3F-42C2-BE7B-784768EC6759}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{048F5366-5815-45AD-B58B-7F6BB7670C40}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -7990,13 +7990,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC9CBB06-5AC2-431B-AFA2-BA6F4132E581}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4B6E1BD-F7A0-4FDC-88AD-1CB959A4F642}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{963FA2E2-53B5-4F5F-B80F-05476EE4A892}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF3C16E3-0DA4-4F89-B6D9-5EE4330746ED}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{048F5366-5815-45AD-B58B-7F6BB7670C40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E055BCF9-3E96-4617-B3D0-B2B16E1889B4}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -7990,13 +7990,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4B6E1BD-F7A0-4FDC-88AD-1CB959A4F642}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09F5B2B0-F1E1-4331-B0E3-F242F32A0768}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF3C16E3-0DA4-4F89-B6D9-5EE4330746ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2734F735-2931-471F-B78B-03BCE93B17B6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E055BCF9-3E96-4617-B3D0-B2B16E1889B4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD52E7AB-2029-4615-9582-C27EB00D28C0}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -7990,13 +7990,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09F5B2B0-F1E1-4331-B0E3-F242F32A0768}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29B1C51C-A7B9-470B-8C15-9746FA17C53F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2734F735-2931-471F-B78B-03BCE93B17B6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97FB2F7B-F5F2-4B81-A24E-6D18505F1E7A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD52E7AB-2029-4615-9582-C27EB00D28C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7375B383-5A4D-4A4D-90D5-870911F4AC82}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -7990,13 +7990,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29B1C51C-A7B9-470B-8C15-9746FA17C53F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CA46AAF-00DA-41D2-A722-46C1099195CF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97FB2F7B-F5F2-4B81-A24E-6D18505F1E7A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{123FB197-3508-474D-B1E5-73F844194B14}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7375B383-5A4D-4A4D-90D5-870911F4AC82}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B81EA90-F889-40DD-B78A-416825BFD01F}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -7712,291 +7712,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CA46AAF-00DA-41D2-A722-46C1099195CF}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{123FB197-3508-474D-B1E5-73F844194B14}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B81EA90-F889-40DD-B78A-416825BFD01F}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -7712,4 +7712,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10503867-2B97-48D4-9A13-B1B4E9EE014D}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9AB7A29-039A-47F0-B2F2-51DC50BB12DA}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D05546AD-712C-4EF3-AE67-654B7A2920F2}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -7990,13 +7990,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10503867-2B97-48D4-9A13-B1B4E9EE014D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BB0EE23-8818-4187-9724-F0455BE14AE4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9AB7A29-039A-47F0-B2F2-51DC50BB12DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DF3C2FE-41DC-4CD3-B9E4-94780936EFDA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D05546AD-712C-4EF3-AE67-654B7A2920F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E436B68-DB93-4A08-8803-8B0E21041EF7}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -7990,13 +7990,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BB0EE23-8818-4187-9724-F0455BE14AE4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04F0663B-0F8E-4525-8EB1-D55C92388CA8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DF3C2FE-41DC-4CD3-B9E4-94780936EFDA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3536975F-6799-4727-954C-D898C0201354}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E436B68-DB93-4A08-8803-8B0E21041EF7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3A7B32B-37D2-4E22-883B-43C7253D2EFD}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -7990,13 +7990,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04F0663B-0F8E-4525-8EB1-D55C92388CA8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A3CA018-C671-4ED0-B4A4-736F772384A0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3536975F-6799-4727-954C-D898C0201354}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AD6B3FC-9A35-408F-873E-E146769B9F2E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3A7B32B-37D2-4E22-883B-43C7253D2EFD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A014ABE3-BA53-408A-B2BA-B69098D00A95}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -7990,13 +7990,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A3CA018-C671-4ED0-B4A4-736F772384A0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A39EA7A-17DA-4BC8-A1A7-8DB41076BCB4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AD6B3FC-9A35-408F-873E-E146769B9F2E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4EF0DD0-622E-41DA-A0D6-C6E32D0C3D98}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A014ABE3-BA53-408A-B2BA-B69098D00A95}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEDB0E13-F2CA-4D59-9C07-9A7655BDFC95}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -7990,13 +7990,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A39EA7A-17DA-4BC8-A1A7-8DB41076BCB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97194822-02AB-44D1-AC77-496D0FC7FD8F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4EF0DD0-622E-41DA-A0D6-C6E32D0C3D98}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{175717F8-916E-4996-866E-CCF56A2DD25F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEDB0E13-F2CA-4D59-9C07-9A7655BDFC95}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E150AAC3-0DAB-46D3-9C49-CBCE18EB81C4}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -7712,291 +7712,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97194822-02AB-44D1-AC77-496D0FC7FD8F}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{175717F8-916E-4996-866E-CCF56A2DD25F}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E150AAC3-0DAB-46D3-9C49-CBCE18EB81C4}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -7712,4 +7712,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26F940C0-C2AC-4436-B83E-EDDE5D1DA164}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{565D2F8D-301E-4570-8099-9D1F1BD44554}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A55A2E7D-B702-4540-BDD7-ECD195090435}"/>
 </file>